--- a/sources/eddy_step8b.xlsx
+++ b/sources/eddy_step8b.xlsx
@@ -862,6 +862,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
@@ -924,6 +929,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
@@ -984,6 +994,11 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>89b9a62a-0e17-41f7-9bcd-95c83f81b48a</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -16860,6 +16875,11 @@
           <t>mmmhhmmmhmmm</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
@@ -16907,6 +16927,11 @@
           <t>mmmhhL</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
@@ -16937,6 +16962,11 @@
       <c r="T188" t="inlineStr">
         <is>
           <t>mmmhhL</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>b321b883-5528-4383-9e3a-01d93e60f6ab</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
